--- a/assets/afl_players_2026.xlsx
+++ b/assets/afl_players_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\FlutterProjects\my_app\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91CF3758-DFC8-4375-AC6A-63FA0E2C9FD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{384DA9C4-8FF5-4306-8971-FEC38C396AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4605" yWindow="1005" windowWidth="25905" windowHeight="20760" xr2:uid="{665E5CEE-4E8C-4944-8463-360E9D61C4FF}"/>
+    <workbookView xWindow="885" yWindow="720" windowWidth="24465" windowHeight="19590" xr2:uid="{665E5CEE-4E8C-4944-8463-360E9D61C4FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1554" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="797">
   <si>
     <t>Chayce Jones</t>
   </si>
@@ -2424,6 +2424,12 @@
   </si>
   <si>
     <t>GWS GIants</t>
+  </si>
+  <si>
+    <t>Elijah Hollands</t>
+  </si>
+  <si>
+    <t>Wade Derkens</t>
   </si>
 </sst>
 </file>
@@ -2838,7 +2844,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E4E5FAF-ED52-4998-8EA2-2EBE5839156D}">
-  <dimension ref="A1:D776"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:D778"/>
   <sheetFormatPr defaultColWidth="16.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25" style="1" bestFit="1" customWidth="1"/>
@@ -2860,7 +2867,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2874,7 +2881,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -2888,7 +2895,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -2902,7 +2909,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
@@ -2916,7 +2923,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -2930,7 +2937,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -2944,7 +2951,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -2958,7 +2965,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -2972,7 +2979,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -2986,7 +2993,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -3000,7 +3007,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -3014,7 +3021,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -3028,7 +3035,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
@@ -3042,7 +3049,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
@@ -3056,7 +3063,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -3070,7 +3077,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -3084,7 +3091,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
@@ -3098,7 +3105,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -3112,7 +3119,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
@@ -3126,7 +3133,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
@@ -3140,7 +3147,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
@@ -3154,7 +3161,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -3168,7 +3175,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -3182,7 +3189,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -3196,7 +3203,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
@@ -3210,7 +3217,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -3224,7 +3231,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>26</v>
       </c>
@@ -3238,7 +3245,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>27</v>
       </c>
@@ -3252,7 +3259,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>28</v>
       </c>
@@ -3266,7 +3273,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>29</v>
       </c>
@@ -3280,7 +3287,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>30</v>
       </c>
@@ -3294,7 +3301,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>31</v>
       </c>
@@ -3308,7 +3315,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>32</v>
       </c>
@@ -3322,7 +3329,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>33</v>
       </c>
@@ -3336,7 +3343,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
@@ -3350,7 +3357,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>35</v>
       </c>
@@ -3364,7 +3371,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>36</v>
       </c>
@@ -3378,7 +3385,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
@@ -3389,7 +3396,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>38</v>
       </c>
@@ -3400,7 +3407,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>39</v>
       </c>
@@ -3411,7 +3418,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>40</v>
       </c>
@@ -3422,7 +3429,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
@@ -3436,7 +3443,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
@@ -3450,7 +3457,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -3464,7 +3471,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -3478,7 +3485,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
@@ -3492,7 +3499,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
@@ -3506,7 +3513,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
@@ -3520,7 +3527,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
@@ -3534,7 +3541,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -3548,7 +3555,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
@@ -3562,7 +3569,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
@@ -3576,7 +3583,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
@@ -3590,7 +3597,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
@@ -3604,7 +3611,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
@@ -3618,7 +3625,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
@@ -3632,7 +3639,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
@@ -3646,7 +3653,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
@@ -3660,7 +3667,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
@@ -3674,7 +3681,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
@@ -3688,7 +3695,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
@@ -3702,7 +3709,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>63</v>
       </c>
@@ -3716,7 +3723,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
@@ -3730,7 +3737,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
@@ -3744,7 +3751,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
@@ -3758,7 +3765,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
@@ -3772,7 +3779,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>68</v>
       </c>
@@ -3786,7 +3793,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
@@ -3800,7 +3807,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>70</v>
       </c>
@@ -3814,7 +3821,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
@@ -3828,7 +3835,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>72</v>
       </c>
@@ -3842,7 +3849,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>73</v>
       </c>
@@ -3856,7 +3863,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>74</v>
       </c>
@@ -3870,7 +3877,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
@@ -3884,7 +3891,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>76</v>
       </c>
@@ -3898,7 +3905,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>77</v>
       </c>
@@ -3912,7 +3919,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>78</v>
       </c>
@@ -3926,7 +3933,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
@@ -3940,7 +3947,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>80</v>
       </c>
@@ -3951,7 +3958,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>81</v>
       </c>
@@ -3962,7 +3969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>82</v>
       </c>
@@ -3973,7 +3980,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>83</v>
       </c>
@@ -3984,7 +3991,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>84</v>
       </c>
@@ -3995,7 +4002,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>85</v>
       </c>
@@ -4006,499 +4013,484 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C86" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D86">
         <v>2026</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="B87" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C87" s="1">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="D87">
         <v>2026</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C88" s="1">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D88">
         <v>2026</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>89</v>
+        <v>122</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C89" s="1">
-        <v>5</v>
-      </c>
       <c r="D89">
         <v>2026</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C90" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D90">
         <v>2026</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>91</v>
+        <v>111</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C91" s="1">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D91">
         <v>2026</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C92" s="1">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D92">
         <v>2026</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C93" s="1">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D93">
         <v>2026</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C94" s="1">
-        <v>10</v>
-      </c>
       <c r="D94">
         <v>2026</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C95" s="1">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D95">
         <v>2026</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>96</v>
+        <v>119</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C96" s="1">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D96">
         <v>2026</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
-        <v>97</v>
+        <v>118</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C97" s="1">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="D97">
         <v>2026</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C98" s="1">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D98">
         <v>2026</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C99" s="1">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D99">
         <v>2026</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C100" s="1">
-        <v>21</v>
-      </c>
       <c r="D100">
         <v>2026</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C101" s="1">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D101">
         <v>2026</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C102" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D102">
         <v>2026</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C103" s="1">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D103">
         <v>2026</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C104" s="1">
-        <v>26</v>
-      </c>
       <c r="D104">
         <v>2026</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C105" s="1">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D105">
         <v>2026</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C106" s="1">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="D106">
         <v>2026</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C107" s="1">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D107">
         <v>2026</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C108" s="1">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D108">
         <v>2026</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
-        <v>109</v>
+        <v>86</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C109" s="1">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>2026</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C110" s="1">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D110">
         <v>2026</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C111" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>2026</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C112" s="1">
-        <v>36</v>
-      </c>
       <c r="D112">
         <v>2026</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C113" s="1">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="D113">
         <v>2026</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C114" s="1">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D114">
         <v>2026</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C115" s="1">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D115">
         <v>2026</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C116" s="1">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D116">
         <v>2026</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C117" s="1">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D117">
         <v>2026</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C118" s="1">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D118">
         <v>2026</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C119" s="1">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D119">
         <v>2026</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>129</v>
       </c>
       <c r="C120" s="1">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D120">
         <v>2026</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>129</v>
@@ -4507,53 +4499,65 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>122</v>
+        <v>88</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="C122" s="1">
+        <v>4</v>
+      </c>
       <c r="D122">
         <v>2026</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="C123" s="1">
+        <v>9</v>
+      </c>
       <c r="D123">
         <v>2026</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="C124" s="1">
+        <v>34</v>
+      </c>
       <c r="D124">
         <v>2026</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
-        <v>125</v>
+        <v>99</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="C125" s="1">
+        <v>18</v>
+      </c>
       <c r="D125">
         <v>2026</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>129</v>
@@ -4562,9 +4566,9 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>129</v>
@@ -4573,18 +4577,21 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>129</v>
       </c>
+      <c r="C128" s="1">
+        <v>6</v>
+      </c>
       <c r="D128">
         <v>2026</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>130</v>
       </c>
@@ -4598,7 +4605,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>131</v>
       </c>
@@ -4612,7 +4619,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>132</v>
       </c>
@@ -4626,7 +4633,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>133</v>
       </c>
@@ -4640,7 +4647,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>134</v>
       </c>
@@ -4654,7 +4661,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>135</v>
       </c>
@@ -4668,7 +4675,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>136</v>
       </c>
@@ -4682,7 +4689,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>137</v>
       </c>
@@ -4696,7 +4703,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>138</v>
       </c>
@@ -4710,7 +4717,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>139</v>
       </c>
@@ -4724,7 +4731,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>140</v>
       </c>
@@ -4738,7 +4745,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
@@ -4752,7 +4759,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>142</v>
       </c>
@@ -4766,7 +4773,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>143</v>
       </c>
@@ -4780,7 +4787,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>144</v>
       </c>
@@ -4794,7 +4801,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>145</v>
       </c>
@@ -4808,7 +4815,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>146</v>
       </c>
@@ -4822,7 +4829,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>147</v>
       </c>
@@ -4836,7 +4843,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>148</v>
       </c>
@@ -4850,7 +4857,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>149</v>
       </c>
@@ -4864,7 +4871,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>150</v>
       </c>
@@ -4878,7 +4885,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>151</v>
       </c>
@@ -4892,7 +4899,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>152</v>
       </c>
@@ -4906,7 +4913,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>153</v>
       </c>
@@ -4920,7 +4927,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>154</v>
       </c>
@@ -4934,7 +4941,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>155</v>
       </c>
@@ -4948,7 +4955,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>156</v>
       </c>
@@ -4962,7 +4969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>157</v>
       </c>
@@ -4976,7 +4983,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>158</v>
       </c>
@@ -4990,7 +4997,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>159</v>
       </c>
@@ -5004,7 +5011,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>160</v>
       </c>
@@ -5018,7 +5025,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>161</v>
       </c>
@@ -5032,7 +5039,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>162</v>
       </c>
@@ -5046,7 +5053,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>163</v>
       </c>
@@ -5060,7 +5067,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>164</v>
       </c>
@@ -5074,7 +5081,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>165</v>
       </c>
@@ -5088,7 +5095,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>166</v>
       </c>
@@ -5102,7 +5109,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>167</v>
       </c>
@@ -5113,7 +5120,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>168</v>
       </c>
@@ -5124,7 +5131,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>169</v>
       </c>
@@ -5135,7 +5142,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>170</v>
       </c>
@@ -5146,7 +5153,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>171</v>
       </c>
@@ -5157,7 +5164,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>172</v>
       </c>
@@ -5168,7 +5175,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>174</v>
       </c>
@@ -5182,7 +5189,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>175</v>
       </c>
@@ -5196,7 +5203,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>176</v>
       </c>
@@ -5210,7 +5217,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>177</v>
       </c>
@@ -5224,7 +5231,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>178</v>
       </c>
@@ -5238,7 +5245,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>179</v>
       </c>
@@ -5252,7 +5259,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>180</v>
       </c>
@@ -5266,7 +5273,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>181</v>
       </c>
@@ -5280,7 +5287,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>182</v>
       </c>
@@ -5294,7 +5301,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>183</v>
       </c>
@@ -5308,7 +5315,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>184</v>
       </c>
@@ -5322,7 +5329,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>185</v>
       </c>
@@ -5336,7 +5343,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>186</v>
       </c>
@@ -5350,7 +5357,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>187</v>
       </c>
@@ -5364,7 +5371,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>188</v>
       </c>
@@ -5378,7 +5385,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>189</v>
       </c>
@@ -5392,7 +5399,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>190</v>
       </c>
@@ -5406,7 +5413,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>191</v>
       </c>
@@ -5420,7 +5427,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>192</v>
       </c>
@@ -5434,7 +5441,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>193</v>
       </c>
@@ -5448,7 +5455,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>194</v>
       </c>
@@ -5462,7 +5469,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>195</v>
       </c>
@@ -5476,7 +5483,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>196</v>
       </c>
@@ -5490,7 +5497,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>197</v>
       </c>
@@ -5504,7 +5511,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>198</v>
       </c>
@@ -5518,7 +5525,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>199</v>
       </c>
@@ -5532,7 +5539,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>200</v>
       </c>
@@ -5546,7 +5553,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>201</v>
       </c>
@@ -5560,7 +5567,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>202</v>
       </c>
@@ -5574,7 +5581,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>203</v>
       </c>
@@ -5588,7 +5595,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>204</v>
       </c>
@@ -5602,7 +5609,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>205</v>
       </c>
@@ -5616,7 +5623,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>206</v>
       </c>
@@ -5630,7 +5637,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>207</v>
       </c>
@@ -5644,7 +5651,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>208</v>
       </c>
@@ -5658,7 +5665,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>209</v>
       </c>
@@ -5672,7 +5679,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>210</v>
       </c>
@@ -5686,7 +5693,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>211</v>
       </c>
@@ -5700,7 +5707,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>212</v>
       </c>
@@ -5711,7 +5718,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>213</v>
       </c>
@@ -5722,7 +5729,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>214</v>
       </c>
@@ -5733,7 +5740,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>215</v>
       </c>
@@ -5744,7 +5751,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>216</v>
       </c>
@@ -5755,7 +5762,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>217</v>
       </c>
@@ -5766,7 +5773,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>218</v>
       </c>
@@ -5780,7 +5787,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>219</v>
       </c>
@@ -5794,7 +5801,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>220</v>
       </c>
@@ -5808,7 +5815,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>221</v>
       </c>
@@ -5822,7 +5829,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>222</v>
       </c>
@@ -5836,7 +5843,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>223</v>
       </c>
@@ -5850,7 +5857,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>224</v>
       </c>
@@ -5864,7 +5871,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>225</v>
       </c>
@@ -5878,7 +5885,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>226</v>
       </c>
@@ -5892,7 +5899,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>227</v>
       </c>
@@ -5906,7 +5913,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>228</v>
       </c>
@@ -5920,7 +5927,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>229</v>
       </c>
@@ -5934,7 +5941,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>230</v>
       </c>
@@ -5948,7 +5955,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>231</v>
       </c>
@@ -5962,7 +5969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>232</v>
       </c>
@@ -5976,7 +5983,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>233</v>
       </c>
@@ -5990,7 +5997,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>234</v>
       </c>
@@ -6004,7 +6011,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>235</v>
       </c>
@@ -6018,7 +6025,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>236</v>
       </c>
@@ -6032,7 +6039,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>237</v>
       </c>
@@ -6046,7 +6053,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>238</v>
       </c>
@@ -6060,7 +6067,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>239</v>
       </c>
@@ -6074,7 +6081,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>240</v>
       </c>
@@ -6088,7 +6095,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>241</v>
       </c>
@@ -6102,7 +6109,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>242</v>
       </c>
@@ -6116,7 +6123,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>243</v>
       </c>
@@ -6130,7 +6137,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>244</v>
       </c>
@@ -6144,7 +6151,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>245</v>
       </c>
@@ -6158,7 +6165,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>246</v>
       </c>
@@ -6172,7 +6179,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>247</v>
       </c>
@@ -6186,7 +6193,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>248</v>
       </c>
@@ -6200,7 +6207,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>249</v>
       </c>
@@ -6214,7 +6221,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>250</v>
       </c>
@@ -6228,7 +6235,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>251</v>
       </c>
@@ -6242,7 +6249,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>252</v>
       </c>
@@ -6256,7 +6263,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>253</v>
       </c>
@@ -6270,7 +6277,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>254</v>
       </c>
@@ -6281,7 +6288,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>255</v>
       </c>
@@ -6292,7 +6299,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>256</v>
       </c>
@@ -6303,7 +6310,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>257</v>
       </c>
@@ -6314,7 +6321,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>258</v>
       </c>
@@ -6325,7 +6332,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>259</v>
       </c>
@@ -6336,7 +6343,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>260</v>
       </c>
@@ -6349,13 +6356,13 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B259" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C259" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D259">
         <v>2026</v>
@@ -6363,13 +6370,13 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
-        <v>262</v>
+        <v>298</v>
       </c>
       <c r="B260" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C260" s="1">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="D260">
         <v>2026</v>
@@ -6377,13 +6384,13 @@
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="B261" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C261" s="1">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="D261">
         <v>2026</v>
@@ -6391,13 +6398,13 @@
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B262" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C262" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D262">
         <v>2026</v>
@@ -6405,13 +6412,13 @@
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B263" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C263" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D263">
         <v>2026</v>
@@ -6419,13 +6426,13 @@
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="B264" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C264" s="1">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="D264">
         <v>2026</v>
@@ -6433,41 +6440,35 @@
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
-        <v>267</v>
+        <v>301</v>
       </c>
       <c r="B265" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C265" s="1">
-        <v>7</v>
-      </c>
       <c r="D265">
         <v>2026</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
-        <v>268</v>
+        <v>303</v>
       </c>
       <c r="B266" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C266" s="1">
-        <v>8</v>
-      </c>
       <c r="D266">
         <v>2026</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B267" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C267" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D267">
         <v>2026</v>
@@ -6475,13 +6476,13 @@
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="B268" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C268" s="1">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D268">
         <v>2026</v>
@@ -6489,13 +6490,13 @@
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B269" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C269" s="1">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D269">
         <v>2026</v>
@@ -6503,13 +6504,13 @@
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="B270" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C270" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D270">
         <v>2026</v>
@@ -6517,13 +6518,13 @@
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B271" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C271" s="1">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D271">
         <v>2026</v>
@@ -6531,27 +6532,24 @@
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
-        <v>274</v>
+        <v>304</v>
       </c>
       <c r="B272" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C272" s="1">
-        <v>14</v>
-      </c>
       <c r="D272">
         <v>2026</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="B273" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C273" s="1">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D273">
         <v>2026</v>
@@ -6559,13 +6557,13 @@
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B274" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C274" s="1">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D274">
         <v>2026</v>
@@ -6573,13 +6571,13 @@
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="B275" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C275" s="1">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D275">
         <v>2026</v>
@@ -6587,27 +6585,24 @@
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B276" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C276" s="1">
-        <v>18</v>
-      </c>
       <c r="D276">
         <v>2026</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="B277" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C277" s="1">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="D277">
         <v>2026</v>
@@ -6615,13 +6610,13 @@
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="B278" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C278" s="1">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D278">
         <v>2026</v>
@@ -6629,13 +6624,13 @@
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="B279" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C279" s="1">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D279">
         <v>2026</v>
@@ -6643,13 +6638,13 @@
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B280" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C280" s="1">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D280">
         <v>2026</v>
@@ -6657,13 +6652,13 @@
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B281" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C281" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D281">
         <v>2026</v>
@@ -6671,13 +6666,13 @@
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="B282" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C282" s="1">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D282">
         <v>2026</v>
@@ -6685,13 +6680,13 @@
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="B283" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C283" s="1">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D283">
         <v>2026</v>
@@ -6699,13 +6694,13 @@
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="B284" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C284" s="1">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="D284">
         <v>2026</v>
@@ -6713,13 +6708,13 @@
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B285" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C285" s="1">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D285">
         <v>2026</v>
@@ -6727,13 +6722,13 @@
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
-        <v>288</v>
+        <v>270</v>
       </c>
       <c r="B286" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C286" s="1">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="D286">
         <v>2026</v>
@@ -6741,27 +6736,24 @@
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
-        <v>289</v>
+        <v>302</v>
       </c>
       <c r="B287" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="C287" s="1">
-        <v>34</v>
-      </c>
       <c r="D287">
         <v>2026</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B288" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C288" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D288">
         <v>2026</v>
@@ -6769,13 +6761,13 @@
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B289" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C289" s="1">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D289">
         <v>2026</v>
@@ -6783,13 +6775,13 @@
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="B290" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C290" s="1">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D290">
         <v>2026</v>
@@ -6797,13 +6789,13 @@
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B291" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C291" s="1">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D291">
         <v>2026</v>
@@ -6811,13 +6803,13 @@
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B292" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C292" s="1">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="D292">
         <v>2026</v>
@@ -6825,13 +6817,13 @@
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="B293" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C293" s="1">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D293">
         <v>2026</v>
@@ -6839,13 +6831,13 @@
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="B294" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C294" s="1">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="D294">
         <v>2026</v>
@@ -6853,13 +6845,13 @@
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="B295" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C295" s="1">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D295">
         <v>2026</v>
@@ -6867,13 +6859,13 @@
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="B296" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C296" s="1">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D296">
         <v>2026</v>
@@ -6881,13 +6873,13 @@
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
-        <v>299</v>
+        <v>264</v>
       </c>
       <c r="B297" s="1" t="s">
         <v>793</v>
       </c>
       <c r="C297" s="1">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="D297">
         <v>2026</v>
@@ -6895,60 +6887,75 @@
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
-        <v>300</v>
+        <v>266</v>
       </c>
       <c r="B298" s="1" t="s">
         <v>793</v>
       </c>
+      <c r="C298" s="1">
+        <v>6</v>
+      </c>
       <c r="D298">
         <v>2026</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="B299" s="1" t="s">
         <v>793</v>
       </c>
+      <c r="C299" s="1">
+        <v>30</v>
+      </c>
       <c r="D299">
         <v>2026</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B300" s="1" t="s">
         <v>793</v>
       </c>
+      <c r="C300" s="1">
+        <v>44</v>
+      </c>
       <c r="D300">
         <v>2026</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
-        <v>303</v>
+        <v>278</v>
       </c>
       <c r="B301" s="1" t="s">
         <v>793</v>
       </c>
+      <c r="C301" s="1">
+        <v>18</v>
+      </c>
       <c r="D301">
         <v>2026</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B302" s="1" t="s">
         <v>793</v>
       </c>
+      <c r="C302" s="1">
+        <v>39</v>
+      </c>
       <c r="D302">
         <v>2026</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>305</v>
       </c>
@@ -6962,7 +6969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>306</v>
       </c>
@@ -6976,7 +6983,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>307</v>
       </c>
@@ -6990,7 +6997,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>308</v>
       </c>
@@ -7004,7 +7011,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>309</v>
       </c>
@@ -7018,7 +7025,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>310</v>
       </c>
@@ -7032,7 +7039,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>311</v>
       </c>
@@ -7046,7 +7053,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>312</v>
       </c>
@@ -7060,7 +7067,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>313</v>
       </c>
@@ -7074,7 +7081,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>314</v>
       </c>
@@ -7088,7 +7095,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>315</v>
       </c>
@@ -7102,7 +7109,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>316</v>
       </c>
@@ -7116,7 +7123,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>317</v>
       </c>
@@ -7130,7 +7137,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>318</v>
       </c>
@@ -7144,7 +7151,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>319</v>
       </c>
@@ -7158,7 +7165,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>320</v>
       </c>
@@ -7172,7 +7179,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>321</v>
       </c>
@@ -7186,7 +7193,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>322</v>
       </c>
@@ -7200,7 +7207,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>323</v>
       </c>
@@ -7214,7 +7221,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>324</v>
       </c>
@@ -7228,7 +7235,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>325</v>
       </c>
@@ -7242,7 +7249,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>326</v>
       </c>
@@ -7256,7 +7263,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>327</v>
       </c>
@@ -7270,7 +7277,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>328</v>
       </c>
@@ -7284,7 +7291,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>329</v>
       </c>
@@ -7298,7 +7305,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>330</v>
       </c>
@@ -7312,7 +7319,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>331</v>
       </c>
@@ -7326,7 +7333,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>332</v>
       </c>
@@ -7340,7 +7347,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>333</v>
       </c>
@@ -7354,7 +7361,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>334</v>
       </c>
@@ -7368,7 +7375,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>335</v>
       </c>
@@ -7382,7 +7389,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>336</v>
       </c>
@@ -7396,7 +7403,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>337</v>
       </c>
@@ -7410,7 +7417,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>338</v>
       </c>
@@ -7424,7 +7431,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>339</v>
       </c>
@@ -7438,7 +7445,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>340</v>
       </c>
@@ -7452,7 +7459,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>341</v>
       </c>
@@ -7463,7 +7470,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>342</v>
       </c>
@@ -7474,7 +7481,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>343</v>
       </c>
@@ -7485,7 +7492,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>344</v>
       </c>
@@ -7496,7 +7503,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>345</v>
       </c>
@@ -7507,7 +7514,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>346</v>
       </c>
@@ -7518,7 +7525,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>347</v>
       </c>
@@ -7529,7 +7536,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>348</v>
       </c>
@@ -7540,7 +7547,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>349</v>
       </c>
@@ -7554,7 +7561,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>350</v>
       </c>
@@ -7568,7 +7575,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>351</v>
       </c>
@@ -7582,7 +7589,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>352</v>
       </c>
@@ -7596,7 +7603,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>353</v>
       </c>
@@ -7610,7 +7617,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>354</v>
       </c>
@@ -7624,7 +7631,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>355</v>
       </c>
@@ -7638,7 +7645,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>356</v>
       </c>
@@ -7652,7 +7659,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>357</v>
       </c>
@@ -7666,7 +7673,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>358</v>
       </c>
@@ -7680,7 +7687,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>359</v>
       </c>
@@ -7694,7 +7701,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>360</v>
       </c>
@@ -7708,7 +7715,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>361</v>
       </c>
@@ -7722,7 +7729,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>362</v>
       </c>
@@ -7736,7 +7743,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>363</v>
       </c>
@@ -7750,7 +7757,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>364</v>
       </c>
@@ -7764,7 +7771,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>365</v>
       </c>
@@ -7778,7 +7785,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>366</v>
       </c>
@@ -7792,7 +7799,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>367</v>
       </c>
@@ -7806,7 +7813,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>368</v>
       </c>
@@ -7820,7 +7827,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>369</v>
       </c>
@@ -7834,7 +7841,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>370</v>
       </c>
@@ -7848,7 +7855,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>371</v>
       </c>
@@ -7862,7 +7869,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>372</v>
       </c>
@@ -7876,7 +7883,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>373</v>
       </c>
@@ -7890,7 +7897,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>374</v>
       </c>
@@ -7904,7 +7911,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>375</v>
       </c>
@@ -7918,7 +7925,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>376</v>
       </c>
@@ -7932,7 +7939,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>377</v>
       </c>
@@ -7946,7 +7953,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>378</v>
       </c>
@@ -7960,7 +7967,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>379</v>
       </c>
@@ -7974,7 +7981,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>380</v>
       </c>
@@ -7988,7 +7995,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>381</v>
       </c>
@@ -8002,7 +8009,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>382</v>
       </c>
@@ -8016,7 +8023,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>383</v>
       </c>
@@ -8030,7 +8037,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>384</v>
       </c>
@@ -8044,7 +8051,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>385</v>
       </c>
@@ -8058,7 +8065,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>386</v>
       </c>
@@ -8072,7 +8079,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>387</v>
       </c>
@@ -8086,7 +8093,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>388</v>
       </c>
@@ -8097,7 +8104,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>389</v>
       </c>
@@ -8108,7 +8115,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>390</v>
       </c>
@@ -8119,7 +8126,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
         <v>391</v>
       </c>
@@ -8130,7 +8137,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
         <v>392</v>
       </c>
@@ -8141,7 +8148,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>393</v>
       </c>
@@ -8155,7 +8162,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>394</v>
       </c>
@@ -8169,7 +8176,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>395</v>
       </c>
@@ -8183,7 +8190,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>396</v>
       </c>
@@ -8197,7 +8204,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>397</v>
       </c>
@@ -8211,7 +8218,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>398</v>
       </c>
@@ -8225,7 +8232,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>399</v>
       </c>
@@ -8239,7 +8246,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>400</v>
       </c>
@@ -8253,7 +8260,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>401</v>
       </c>
@@ -8267,7 +8274,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>402</v>
       </c>
@@ -8281,7 +8288,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>403</v>
       </c>
@@ -8295,7 +8302,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>404</v>
       </c>
@@ -8309,7 +8316,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
         <v>405</v>
       </c>
@@ -8323,7 +8330,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
         <v>406</v>
       </c>
@@ -8337,7 +8344,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>407</v>
       </c>
@@ -8351,7 +8358,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>408</v>
       </c>
@@ -8365,7 +8372,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>409</v>
       </c>
@@ -8379,7 +8386,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>410</v>
       </c>
@@ -8393,7 +8400,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>411</v>
       </c>
@@ -8407,7 +8414,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>412</v>
       </c>
@@ -8421,7 +8428,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>413</v>
       </c>
@@ -8435,7 +8442,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>414</v>
       </c>
@@ -8449,7 +8456,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>415</v>
       </c>
@@ -8463,7 +8470,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>416</v>
       </c>
@@ -8477,7 +8484,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>417</v>
       </c>
@@ -8491,7 +8498,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>418</v>
       </c>
@@ -8505,7 +8512,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>419</v>
       </c>
@@ -8519,7 +8526,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>420</v>
       </c>
@@ -8533,7 +8540,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>421</v>
       </c>
@@ -8547,7 +8554,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>422</v>
       </c>
@@ -8561,7 +8568,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>423</v>
       </c>
@@ -8575,7 +8582,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>424</v>
       </c>
@@ -8589,7 +8596,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="423" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>425</v>
       </c>
@@ -8603,7 +8610,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>426</v>
       </c>
@@ -8617,7 +8624,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="425" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>427</v>
       </c>
@@ -8631,7 +8638,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="426" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>428</v>
       </c>
@@ -8645,7 +8652,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="427" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>429</v>
       </c>
@@ -8659,7 +8666,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>430</v>
       </c>
@@ -8670,7 +8677,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>431</v>
       </c>
@@ -8681,7 +8688,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>432</v>
       </c>
@@ -8692,7 +8699,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>433</v>
       </c>
@@ -8703,7 +8710,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>434</v>
       </c>
@@ -8714,7 +8721,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>435</v>
       </c>
@@ -8728,7 +8735,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>436</v>
       </c>
@@ -8742,7 +8749,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>437</v>
       </c>
@@ -8756,7 +8763,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>438</v>
       </c>
@@ -8770,7 +8777,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>439</v>
       </c>
@@ -8784,7 +8791,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>440</v>
       </c>
@@ -8798,7 +8805,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>441</v>
       </c>
@@ -8812,7 +8819,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="440" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>442</v>
       </c>
@@ -8826,7 +8833,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="441" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>443</v>
       </c>
@@ -8840,7 +8847,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="442" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>444</v>
       </c>
@@ -8854,7 +8861,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="443" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>445</v>
       </c>
@@ -8868,7 +8875,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="444" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>446</v>
       </c>
@@ -8882,7 +8889,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="445" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>447</v>
       </c>
@@ -8896,7 +8903,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="446" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>448</v>
       </c>
@@ -8910,7 +8917,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="447" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>449</v>
       </c>
@@ -8924,7 +8931,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="448" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>450</v>
       </c>
@@ -8938,7 +8945,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="449" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>451</v>
       </c>
@@ -8952,7 +8959,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="450" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>452</v>
       </c>
@@ -8966,7 +8973,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="451" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>453</v>
       </c>
@@ -8980,7 +8987,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="452" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>454</v>
       </c>
@@ -8994,7 +9001,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="453" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>455</v>
       </c>
@@ -9008,7 +9015,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="454" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>456</v>
       </c>
@@ -9022,7 +9029,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="455" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>457</v>
       </c>
@@ -9036,7 +9043,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="456" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>458</v>
       </c>
@@ -9050,7 +9057,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="457" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>459</v>
       </c>
@@ -9064,7 +9071,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="458" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>460</v>
       </c>
@@ -9078,7 +9085,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="459" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>461</v>
       </c>
@@ -9092,7 +9099,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="460" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>462</v>
       </c>
@@ -9106,7 +9113,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="461" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>463</v>
       </c>
@@ -9120,7 +9127,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="462" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>464</v>
       </c>
@@ -9134,7 +9141,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="463" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>465</v>
       </c>
@@ -9148,7 +9155,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="464" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>466</v>
       </c>
@@ -9162,7 +9169,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="465" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>467</v>
       </c>
@@ -9176,7 +9183,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="466" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>468</v>
       </c>
@@ -9190,7 +9197,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="467" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>469</v>
       </c>
@@ -9201,7 +9208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="468" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>470</v>
       </c>
@@ -9212,7 +9219,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="469" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>471</v>
       </c>
@@ -9223,7 +9230,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="470" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>472</v>
       </c>
@@ -9234,7 +9241,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="471" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>473</v>
       </c>
@@ -9245,7 +9252,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="472" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>474</v>
       </c>
@@ -9256,7 +9263,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="473" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>475</v>
       </c>
@@ -9267,7 +9274,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="474" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>476</v>
       </c>
@@ -9278,7 +9285,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="475" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>477</v>
       </c>
@@ -9289,7 +9296,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="476" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>478</v>
       </c>
@@ -9303,7 +9310,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="477" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>479</v>
       </c>
@@ -9317,7 +9324,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="478" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>480</v>
       </c>
@@ -9331,7 +9338,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="479" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>481</v>
       </c>
@@ -9345,7 +9352,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="480" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>482</v>
       </c>
@@ -9359,7 +9366,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="481" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>483</v>
       </c>
@@ -9373,7 +9380,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="482" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>484</v>
       </c>
@@ -9387,7 +9394,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="483" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>485</v>
       </c>
@@ -9401,7 +9408,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="484" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>486</v>
       </c>
@@ -9415,7 +9422,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="485" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>487</v>
       </c>
@@ -9429,7 +9436,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="486" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>488</v>
       </c>
@@ -9443,7 +9450,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="487" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>489</v>
       </c>
@@ -9457,7 +9464,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="488" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>490</v>
       </c>
@@ -9471,7 +9478,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="489" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>491</v>
       </c>
@@ -9485,7 +9492,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="490" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>492</v>
       </c>
@@ -9499,7 +9506,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="491" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>493</v>
       </c>
@@ -9513,7 +9520,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="492" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>494</v>
       </c>
@@ -9527,7 +9534,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="493" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>495</v>
       </c>
@@ -9541,7 +9548,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="494" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>496</v>
       </c>
@@ -9555,7 +9562,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="495" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>497</v>
       </c>
@@ -9569,7 +9576,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="496" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>498</v>
       </c>
@@ -9583,7 +9590,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>499</v>
       </c>
@@ -9597,7 +9604,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>500</v>
       </c>
@@ -9611,7 +9618,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>501</v>
       </c>
@@ -9625,7 +9632,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>502</v>
       </c>
@@ -9639,7 +9646,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>503</v>
       </c>
@@ -9653,7 +9660,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>504</v>
       </c>
@@ -9667,7 +9674,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>505</v>
       </c>
@@ -9681,7 +9688,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>506</v>
       </c>
@@ -9695,7 +9702,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>507</v>
       </c>
@@ -9709,7 +9716,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>508</v>
       </c>
@@ -9723,7 +9730,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>509</v>
       </c>
@@ -9737,7 +9744,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>510</v>
       </c>
@@ -9751,7 +9758,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>511</v>
       </c>
@@ -9765,7 +9772,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>512</v>
       </c>
@@ -9779,7 +9786,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>513</v>
       </c>
@@ -9793,7 +9800,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>514</v>
       </c>
@@ -9807,7 +9814,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>515</v>
       </c>
@@ -9821,7 +9828,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>516</v>
       </c>
@@ -9832,7 +9839,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>517</v>
       </c>
@@ -9843,7 +9850,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>518</v>
       </c>
@@ -9854,7 +9861,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>519</v>
       </c>
@@ -9865,7 +9872,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>520</v>
       </c>
@@ -9879,7 +9886,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>521</v>
       </c>
@@ -9893,7 +9900,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>522</v>
       </c>
@@ -9907,7 +9914,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>523</v>
       </c>
@@ -9921,7 +9928,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>524</v>
       </c>
@@ -9935,7 +9942,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>525</v>
       </c>
@@ -9949,7 +9956,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>526</v>
       </c>
@@ -9963,7 +9970,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
         <v>527</v>
       </c>
@@ -9977,7 +9984,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
         <v>528</v>
       </c>
@@ -9991,7 +9998,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>529</v>
       </c>
@@ -10005,7 +10012,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="528" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>530</v>
       </c>
@@ -10019,7 +10026,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="529" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>531</v>
       </c>
@@ -10033,7 +10040,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="530" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>532</v>
       </c>
@@ -10047,7 +10054,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="531" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>533</v>
       </c>
@@ -10061,7 +10068,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="532" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>534</v>
       </c>
@@ -10075,7 +10082,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="533" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>535</v>
       </c>
@@ -10089,7 +10096,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="534" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>536</v>
       </c>
@@ -10103,7 +10110,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="535" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>537</v>
       </c>
@@ -10117,7 +10124,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="536" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>538</v>
       </c>
@@ -10131,7 +10138,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="537" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>539</v>
       </c>
@@ -10145,7 +10152,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="538" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>540</v>
       </c>
@@ -10159,7 +10166,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="539" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>541</v>
       </c>
@@ -10173,7 +10180,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="540" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>542</v>
       </c>
@@ -10187,7 +10194,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="541" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>543</v>
       </c>
@@ -10201,7 +10208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="542" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>544</v>
       </c>
@@ -10215,7 +10222,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="543" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>545</v>
       </c>
@@ -10229,7 +10236,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="544" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>546</v>
       </c>
@@ -10243,7 +10250,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="545" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>547</v>
       </c>
@@ -10257,7 +10264,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="546" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>548</v>
       </c>
@@ -10271,7 +10278,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="547" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>549</v>
       </c>
@@ -10285,7 +10292,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="548" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>550</v>
       </c>
@@ -10299,7 +10306,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="549" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>551</v>
       </c>
@@ -10313,7 +10320,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="550" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>552</v>
       </c>
@@ -10327,7 +10334,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="551" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>553</v>
       </c>
@@ -10341,7 +10348,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="552" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>554</v>
       </c>
@@ -10355,7 +10362,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="553" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>555</v>
       </c>
@@ -10369,7 +10376,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="554" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>556</v>
       </c>
@@ -10383,7 +10390,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="555" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>557</v>
       </c>
@@ -10397,7 +10404,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="556" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>558</v>
       </c>
@@ -10408,7 +10415,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="557" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>559</v>
       </c>
@@ -10419,7 +10426,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="558" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>560</v>
       </c>
@@ -10430,7 +10437,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="559" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>561</v>
       </c>
@@ -10441,7 +10448,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="560" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>562</v>
       </c>
@@ -10455,7 +10462,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="561" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>563</v>
       </c>
@@ -10469,7 +10476,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="562" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>564</v>
       </c>
@@ -10483,7 +10490,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="563" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>565</v>
       </c>
@@ -10497,7 +10504,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="564" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>566</v>
       </c>
@@ -10511,7 +10518,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="565" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>567</v>
       </c>
@@ -10525,7 +10532,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="566" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>568</v>
       </c>
@@ -10539,7 +10546,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="567" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>569</v>
       </c>
@@ -10553,7 +10560,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="568" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>570</v>
       </c>
@@ -10567,7 +10574,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="569" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>571</v>
       </c>
@@ -10581,7 +10588,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="570" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>572</v>
       </c>
@@ -10595,7 +10602,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="571" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
         <v>573</v>
       </c>
@@ -10609,7 +10616,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="572" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
         <v>574</v>
       </c>
@@ -10623,7 +10630,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="573" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>575</v>
       </c>
@@ -10637,7 +10644,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="574" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>576</v>
       </c>
@@ -10651,7 +10658,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="575" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>577</v>
       </c>
@@ -10665,7 +10672,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="576" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>578</v>
       </c>
@@ -10679,7 +10686,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="577" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>579</v>
       </c>
@@ -10693,7 +10700,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="578" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>580</v>
       </c>
@@ -10707,7 +10714,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="579" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>581</v>
       </c>
@@ -10721,7 +10728,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="580" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>582</v>
       </c>
@@ -10735,7 +10742,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="581" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>583</v>
       </c>
@@ -10749,7 +10756,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="582" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>584</v>
       </c>
@@ -10763,7 +10770,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="583" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>585</v>
       </c>
@@ -10777,7 +10784,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="584" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>586</v>
       </c>
@@ -10791,7 +10798,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="585" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>587</v>
       </c>
@@ -10805,7 +10812,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="586" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>588</v>
       </c>
@@ -10819,7 +10826,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="587" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>589</v>
       </c>
@@ -10833,7 +10840,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="588" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>590</v>
       </c>
@@ -10847,7 +10854,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="589" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>591</v>
       </c>
@@ -10861,7 +10868,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="590" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>592</v>
       </c>
@@ -10875,7 +10882,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="591" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>593</v>
       </c>
@@ -10889,7 +10896,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="592" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>594</v>
       </c>
@@ -10903,7 +10910,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="593" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>595</v>
       </c>
@@ -10917,7 +10924,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="594" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>596</v>
       </c>
@@ -10931,7 +10938,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="595" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>597</v>
       </c>
@@ -10945,7 +10952,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="596" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>598</v>
       </c>
@@ -10959,7 +10966,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="597" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>599</v>
       </c>
@@ -10970,7 +10977,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="598" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>600</v>
       </c>
@@ -10981,7 +10988,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="599" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>601</v>
       </c>
@@ -10992,7 +10999,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="600" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>602</v>
       </c>
@@ -11003,7 +11010,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="601" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>603</v>
       </c>
@@ -11014,7 +11021,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="602" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>604</v>
       </c>
@@ -11028,7 +11035,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="603" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>605</v>
       </c>
@@ -11042,7 +11049,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="604" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>606</v>
       </c>
@@ -11056,7 +11063,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="605" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>607</v>
       </c>
@@ -11070,7 +11077,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="606" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>608</v>
       </c>
@@ -11084,7 +11091,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="607" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>609</v>
       </c>
@@ -11098,7 +11105,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="608" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>610</v>
       </c>
@@ -11112,7 +11119,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="609" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>611</v>
       </c>
@@ -11126,7 +11133,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="610" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>612</v>
       </c>
@@ -11140,7 +11147,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="611" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>613</v>
       </c>
@@ -11154,7 +11161,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="612" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>614</v>
       </c>
@@ -11168,7 +11175,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="613" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>615</v>
       </c>
@@ -11182,7 +11189,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="614" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>616</v>
       </c>
@@ -11196,7 +11203,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="615" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>617</v>
       </c>
@@ -11210,7 +11217,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="616" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>618</v>
       </c>
@@ -11224,7 +11231,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="617" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>619</v>
       </c>
@@ -11238,7 +11245,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="618" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>620</v>
       </c>
@@ -11252,7 +11259,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="619" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>621</v>
       </c>
@@ -11266,7 +11273,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="620" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>622</v>
       </c>
@@ -11280,7 +11287,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="621" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>623</v>
       </c>
@@ -11294,7 +11301,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="622" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>624</v>
       </c>
@@ -11308,7 +11315,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="623" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>625</v>
       </c>
@@ -11322,7 +11329,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="624" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>626</v>
       </c>
@@ -11336,7 +11343,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="625" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>627</v>
       </c>
@@ -11350,7 +11357,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="626" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>628</v>
       </c>
@@ -11364,7 +11371,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="627" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>629</v>
       </c>
@@ -11378,7 +11385,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="628" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>630</v>
       </c>
@@ -11392,7 +11399,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="629" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>631</v>
       </c>
@@ -11406,7 +11413,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="630" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>632</v>
       </c>
@@ -11420,7 +11427,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="631" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>633</v>
       </c>
@@ -11434,7 +11441,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="632" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>634</v>
       </c>
@@ -11448,7 +11455,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="633" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>635</v>
       </c>
@@ -11462,7 +11469,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="634" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>636</v>
       </c>
@@ -11476,7 +11483,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="635" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>637</v>
       </c>
@@ -11490,7 +11497,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="636" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>638</v>
       </c>
@@ -11504,7 +11511,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="637" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>639</v>
       </c>
@@ -11518,7 +11525,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="638" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
         <v>640</v>
       </c>
@@ -11529,7 +11536,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="639" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
         <v>641</v>
       </c>
@@ -11540,7 +11547,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="640" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
         <v>642</v>
       </c>
@@ -11551,7 +11558,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="641" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
         <v>643</v>
       </c>
@@ -11562,7 +11569,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="642" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
         <v>644</v>
       </c>
@@ -11573,7 +11580,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="643" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
         <v>645</v>
       </c>
@@ -11584,7 +11591,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="644" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
         <v>646</v>
       </c>
@@ -11598,7 +11605,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="645" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
         <v>647</v>
       </c>
@@ -11612,7 +11619,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="646" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
         <v>648</v>
       </c>
@@ -11626,7 +11633,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="647" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
         <v>649</v>
       </c>
@@ -11640,7 +11647,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="648" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
         <v>650</v>
       </c>
@@ -11654,7 +11661,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="649" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
         <v>651</v>
       </c>
@@ -11668,7 +11675,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="650" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
         <v>652</v>
       </c>
@@ -11682,7 +11689,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="651" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
         <v>653</v>
       </c>
@@ -11696,7 +11703,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="652" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
         <v>654</v>
       </c>
@@ -11710,7 +11717,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="653" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
         <v>655</v>
       </c>
@@ -11724,7 +11731,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="654" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
         <v>656</v>
       </c>
@@ -11738,7 +11745,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="655" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
         <v>657</v>
       </c>
@@ -11752,7 +11759,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="656" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
         <v>658</v>
       </c>
@@ -11766,7 +11773,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="657" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
         <v>659</v>
       </c>
@@ -11780,7 +11787,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="658" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
         <v>660</v>
       </c>
@@ -11794,7 +11801,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="659" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
         <v>661</v>
       </c>
@@ -11808,7 +11815,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="660" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
         <v>662</v>
       </c>
@@ -11822,7 +11829,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="661" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
         <v>663</v>
       </c>
@@ -11836,7 +11843,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="662" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
         <v>664</v>
       </c>
@@ -11850,7 +11857,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="663" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
         <v>665</v>
       </c>
@@ -11864,7 +11871,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="664" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
         <v>666</v>
       </c>
@@ -11878,7 +11885,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="665" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
         <v>667</v>
       </c>
@@ -11892,7 +11899,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="666" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
         <v>668</v>
       </c>
@@ -11906,7 +11913,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="667" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
         <v>669</v>
       </c>
@@ -11920,7 +11927,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="668" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
         <v>670</v>
       </c>
@@ -11934,7 +11941,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="669" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
         <v>671</v>
       </c>
@@ -11948,7 +11955,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="670" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
         <v>672</v>
       </c>
@@ -11962,7 +11969,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="671" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
         <v>673</v>
       </c>
@@ -11976,7 +11983,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="672" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
         <v>674</v>
       </c>
@@ -11990,7 +11997,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="673" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
         <v>675</v>
       </c>
@@ -12004,7 +12011,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="674" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
         <v>676</v>
       </c>
@@ -12018,7 +12025,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="675" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
         <v>677</v>
       </c>
@@ -12032,7 +12039,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="676" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
         <v>678</v>
       </c>
@@ -12046,7 +12053,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="677" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
         <v>679</v>
       </c>
@@ -12060,7 +12067,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="678" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
         <v>680</v>
       </c>
@@ -12074,7 +12081,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="679" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
         <v>681</v>
       </c>
@@ -12085,7 +12092,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="680" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
         <v>682</v>
       </c>
@@ -12096,7 +12103,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="681" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
         <v>613</v>
       </c>
@@ -12107,7 +12114,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="682" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
         <v>683</v>
       </c>
@@ -12118,7 +12125,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="683" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
         <v>684</v>
       </c>
@@ -12129,7 +12136,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="684" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
         <v>685</v>
       </c>
@@ -12140,7 +12147,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="685" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
         <v>686</v>
       </c>
@@ -12151,7 +12158,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="686" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
         <v>687</v>
       </c>
@@ -12162,7 +12169,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="687" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
         <v>688</v>
       </c>
@@ -12173,7 +12180,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="688" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
         <v>689</v>
       </c>
@@ -12187,7 +12194,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="689" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
         <v>690</v>
       </c>
@@ -12201,7 +12208,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="690" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
         <v>691</v>
       </c>
@@ -12215,7 +12222,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="691" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
         <v>692</v>
       </c>
@@ -12229,7 +12236,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="692" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
         <v>693</v>
       </c>
@@ -12243,7 +12250,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="693" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
         <v>694</v>
       </c>
@@ -12257,7 +12264,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="694" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
         <v>695</v>
       </c>
@@ -12271,7 +12278,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="695" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
         <v>696</v>
       </c>
@@ -12285,7 +12292,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="696" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
         <v>697</v>
       </c>
@@ -12299,7 +12306,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="697" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
         <v>698</v>
       </c>
@@ -12313,7 +12320,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="698" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
         <v>699</v>
       </c>
@@ -12327,7 +12334,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="699" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
         <v>700</v>
       </c>
@@ -12341,7 +12348,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="700" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
         <v>701</v>
       </c>
@@ -12355,7 +12362,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="701" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
         <v>702</v>
       </c>
@@ -12369,7 +12376,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="702" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
         <v>703</v>
       </c>
@@ -12383,7 +12390,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="703" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
         <v>704</v>
       </c>
@@ -12397,7 +12404,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="704" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
         <v>705</v>
       </c>
@@ -12411,7 +12418,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="705" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
         <v>706</v>
       </c>
@@ -12425,7 +12432,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="706" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
         <v>707</v>
       </c>
@@ -12439,7 +12446,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="707" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
         <v>708</v>
       </c>
@@ -12453,7 +12460,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="708" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
         <v>709</v>
       </c>
@@ -12467,7 +12474,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="709" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
         <v>710</v>
       </c>
@@ -12481,7 +12488,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="710" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
         <v>711</v>
       </c>
@@ -12495,7 +12502,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="711" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="1" t="s">
         <v>712</v>
       </c>
@@ -12509,7 +12516,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="712" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="1" t="s">
         <v>713</v>
       </c>
@@ -12523,7 +12530,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="713" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="1" t="s">
         <v>714</v>
       </c>
@@ -12537,7 +12544,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="714" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A714" s="1" t="s">
         <v>715</v>
       </c>
@@ -12551,7 +12558,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="715" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="1" t="s">
         <v>716</v>
       </c>
@@ -12565,7 +12572,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="716" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="1" t="s">
         <v>717</v>
       </c>
@@ -12579,7 +12586,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="717" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="1" t="s">
         <v>718</v>
       </c>
@@ -12593,7 +12600,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="718" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A718" s="1" t="s">
         <v>719</v>
       </c>
@@ -12607,7 +12614,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="719" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="1" t="s">
         <v>720</v>
       </c>
@@ -12621,7 +12628,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="720" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="1" t="s">
         <v>721</v>
       </c>
@@ -12635,7 +12642,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="721" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A721" s="1" t="s">
         <v>722</v>
       </c>
@@ -12649,7 +12656,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="722" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="1" t="s">
         <v>723</v>
       </c>
@@ -12663,7 +12670,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="723" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="1" t="s">
         <v>724</v>
       </c>
@@ -12677,7 +12684,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="724" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="1" t="s">
         <v>725</v>
       </c>
@@ -12688,7 +12695,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="725" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="1" t="s">
         <v>726</v>
       </c>
@@ -12699,7 +12706,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="726" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="1" t="s">
         <v>727</v>
       </c>
@@ -12710,7 +12717,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="727" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="1" t="s">
         <v>728</v>
       </c>
@@ -12721,7 +12728,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="728" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="1" t="s">
         <v>729</v>
       </c>
@@ -12732,7 +12739,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="729" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="1" t="s">
         <v>730</v>
       </c>
@@ -12743,7 +12750,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="730" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="1" t="s">
         <v>731</v>
       </c>
@@ -12754,7 +12761,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="731" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A731" s="1" t="s">
         <v>732</v>
       </c>
@@ -12765,7 +12772,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="732" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="1" t="s">
         <v>733</v>
       </c>
@@ -12776,7 +12783,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="733" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="1" t="s">
         <v>734</v>
       </c>
@@ -12787,7 +12794,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="734" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="1" t="s">
         <v>735</v>
       </c>
@@ -12798,7 +12805,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="735" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="1" t="s">
         <v>736</v>
       </c>
@@ -12812,7 +12819,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="736" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="1" t="s">
         <v>737</v>
       </c>
@@ -12826,7 +12833,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="737" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="1" t="s">
         <v>738</v>
       </c>
@@ -12840,7 +12847,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="738" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="1" t="s">
         <v>739</v>
       </c>
@@ -12854,7 +12861,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="739" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" s="1" t="s">
         <v>740</v>
       </c>
@@ -12868,7 +12875,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="740" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="1" t="s">
         <v>741</v>
       </c>
@@ -12882,7 +12889,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="741" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="1" t="s">
         <v>742</v>
       </c>
@@ -12896,7 +12903,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="742" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="1" t="s">
         <v>743</v>
       </c>
@@ -12910,7 +12917,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="743" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="1" t="s">
         <v>744</v>
       </c>
@@ -12924,7 +12931,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="744" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="1" t="s">
         <v>745</v>
       </c>
@@ -12938,7 +12945,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="745" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="1" t="s">
         <v>746</v>
       </c>
@@ -12952,7 +12959,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="746" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="1" t="s">
         <v>747</v>
       </c>
@@ -12966,7 +12973,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="747" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="1" t="s">
         <v>748</v>
       </c>
@@ -12980,7 +12987,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="748" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="1" t="s">
         <v>749</v>
       </c>
@@ -12994,7 +13001,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="749" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="1" t="s">
         <v>750</v>
       </c>
@@ -13008,7 +13015,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="750" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="1" t="s">
         <v>751</v>
       </c>
@@ -13022,7 +13029,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="751" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="1" t="s">
         <v>752</v>
       </c>
@@ -13036,7 +13043,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="752" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="1" t="s">
         <v>753</v>
       </c>
@@ -13050,7 +13057,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="753" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="1" t="s">
         <v>754</v>
       </c>
@@ -13064,7 +13071,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="754" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="1" t="s">
         <v>755</v>
       </c>
@@ -13078,7 +13085,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="755" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="1" t="s">
         <v>756</v>
       </c>
@@ -13092,7 +13099,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="756" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="1" t="s">
         <v>757</v>
       </c>
@@ -13106,7 +13113,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="757" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="1" t="s">
         <v>758</v>
       </c>
@@ -13120,7 +13127,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="758" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="1" t="s">
         <v>759</v>
       </c>
@@ -13134,7 +13141,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="759" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="1" t="s">
         <v>760</v>
       </c>
@@ -13148,7 +13155,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="760" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="1" t="s">
         <v>761</v>
       </c>
@@ -13162,7 +13169,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="761" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="1" t="s">
         <v>762</v>
       </c>
@@ -13176,7 +13183,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="762" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="1" t="s">
         <v>763</v>
       </c>
@@ -13190,7 +13197,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="763" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="1" t="s">
         <v>713</v>
       </c>
@@ -13204,7 +13211,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="764" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="1" t="s">
         <v>764</v>
       </c>
@@ -13218,7 +13225,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="765" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="1" t="s">
         <v>765</v>
       </c>
@@ -13232,7 +13239,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="766" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="1" t="s">
         <v>766</v>
       </c>
@@ -13246,7 +13253,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="767" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="1" t="s">
         <v>767</v>
       </c>
@@ -13260,7 +13267,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="768" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="1" t="s">
         <v>768</v>
       </c>
@@ -13274,7 +13281,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="769" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="1" t="s">
         <v>769</v>
       </c>
@@ -13288,7 +13295,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="770" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="1" t="s">
         <v>770</v>
       </c>
@@ -13302,7 +13309,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="771" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="1" t="s">
         <v>771</v>
       </c>
@@ -13316,7 +13323,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="772" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="1" t="s">
         <v>772</v>
       </c>
@@ -13330,7 +13337,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="773" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="1" t="s">
         <v>773</v>
       </c>
@@ -13341,7 +13348,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="774" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="1" t="s">
         <v>774</v>
       </c>
@@ -13352,7 +13359,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="775" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="1" t="s">
         <v>775</v>
       </c>
@@ -13363,7 +13370,7 @@
         <v>2026</v>
       </c>
     </row>
-    <row r="776" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="1" t="s">
         <v>776</v>
       </c>
@@ -13374,8 +13381,45 @@
         <v>2026</v>
       </c>
     </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A777" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B777" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C777" s="1">
+        <v>20</v>
+      </c>
+      <c r="D777">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A778" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B778" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C778" s="1">
+        <v>45</v>
+      </c>
+      <c r="D778">
+        <v>2026</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D776" xr:uid="{0E4E5FAF-ED52-4998-8EA2-2EBE5839156D}"/>
+  <autoFilter ref="A1:D776" xr:uid="{0E4E5FAF-ED52-4998-8EA2-2EBE5839156D}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Geelong Cats"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A259:D302">
+      <sortCondition ref="A1:A776"/>
+    </sortState>
+  </autoFilter>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
